--- a/tame_output/ON/bt/strategyON_20240527.xlsx
+++ b/tame_output/ON/bt/strategyON_20240527.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-30.3%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-623.5%</t>
+          <t>-624.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.6%</t>
+          <t>-279.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-26.9%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-20.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.1%</t>
+          <t>-137.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-246.0%</t>
+          <t>-246.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-177.8%</t>
+          <t>-178.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1975"/>
+  <dimension ref="A1:G1976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.834464403548158</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46986,6 +46986,29 @@
       </c>
       <c r="G1975" t="n">
         <v>2.681902311418793</v>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" s="2" t="n">
+        <v>45438</v>
+      </c>
+      <c r="B1976" t="n">
+        <v>3.836023391024959</v>
+      </c>
+      <c r="C1976" t="n">
+        <v>2.813759273265252</v>
+      </c>
+      <c r="D1976" t="n">
+        <v>-4.625761396694592</v>
+      </c>
+      <c r="E1976" t="n">
+        <v>0.963098290273668</v>
+      </c>
+      <c r="F1976" t="n">
+        <v>-0.2265611224062989</v>
+      </c>
+      <c r="G1976" t="n">
+        <v>2.677822599821473</v>
       </c>
     </row>
   </sheetData>
